--- a/data/trans_bre/IP1016-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP1016-Clase-trans_bre.xlsx
@@ -884,7 +884,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,0</t>
+          <t>-2,0; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,73</t>
+          <t>0,0; 5,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
